--- a/ASCal/template.xlsx
+++ b/ASCal/template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbneri\Documents\Visual Studio 2010\Projects\ASCal\ASCal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3a15bcb956f50ef/Documents/Visual Studio 2010/Projects/ASCal/ASCal/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_E9832B07C8135DBF1C83085BBFFB125953A05F18" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E531BFB-AB15-4768-80A8-5065C28361F8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13365" windowHeight="7770" tabRatio="681" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="681" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cal Certificate" sheetId="5" r:id="rId1"/>
@@ -29,24 +30,13 @@
     <definedName name="WET" localSheetId="1">#REF!</definedName>
     <definedName name="WET">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <fileRecoveryPr autoRecover="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="161">
   <si>
     <t>Calibration Certificate</t>
   </si>
@@ -586,9 +576,6 @@
     <t>The instrument was calibrated using reference standard/s traceable to SI Units as maintained by NML-ITDI (Philippines) through SONJU Engineering Services (Philippines)</t>
   </si>
   <si>
-    <t>Busted fused both high and low current</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">3. </t>
     </r>
@@ -616,7 +603,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000000"/>
@@ -3375,10 +3362,10 @@
   <cellStyles count="6">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
-    <cellStyle name="Normal 4" xfId="4"/>
-    <cellStyle name="Normal 5" xfId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Normal 5" xfId="5" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="139">
     <dxf>
@@ -3492,16 +3479,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3542,6 +3519,26 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -3553,16 +3550,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5584,8 +5571,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4738688" y="114300"/>
-          <a:ext cx="2000505" cy="978507"/>
+          <a:off x="4940300" y="114300"/>
+          <a:ext cx="2089405" cy="984857"/>
           <a:chOff x="4701890" y="86590"/>
           <a:chExt cx="2020962" cy="987425"/>
         </a:xfrm>
@@ -6734,9 +6721,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6774,9 +6761,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6811,7 +6798,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -6846,7 +6833,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7019,19 +7006,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AV242"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="20" customWidth="1"/>
-    <col min="3" max="11" width="3.85546875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="5.6640625" style="20" customWidth="1"/>
+    <col min="3" max="11" width="3.88671875" style="20" customWidth="1"/>
     <col min="12" max="12" width="4" style="20" customWidth="1"/>
-    <col min="13" max="13" width="4.140625" style="20" customWidth="1"/>
-    <col min="14" max="26" width="3.85546875" style="20" customWidth="1"/>
+    <col min="13" max="13" width="4.109375" style="20" customWidth="1"/>
+    <col min="14" max="26" width="3.88671875" style="20" customWidth="1"/>
     <col min="27" max="27" width="3" style="20" customWidth="1"/>
-    <col min="28" max="48" width="3.85546875" style="20" hidden="1" customWidth="1"/>
-    <col min="49" max="16384" width="9.140625" style="20" hidden="1"/>
+    <col min="28" max="48" width="3.88671875" style="20" hidden="1" customWidth="1"/>
+    <col min="49" max="16384" width="9.109375" style="20" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:26" ht="12.75" customHeight="1"/>
@@ -7143,7 +7130,7 @@
       <c r="Y10" s="19"/>
       <c r="Z10" s="19"/>
     </row>
-    <row r="11" spans="3:26" ht="12.95" customHeight="1">
+    <row r="11" spans="3:26" ht="12.9" customHeight="1">
       <c r="C11" s="21"/>
       <c r="D11" s="248">
         <f>DataSheet!H27</f>
@@ -7175,7 +7162,7 @@
       <c r="Y11" s="248"/>
       <c r="Z11" s="25"/>
     </row>
-    <row r="12" spans="3:26" ht="12.95" customHeight="1">
+    <row r="12" spans="3:26" ht="12.9" customHeight="1">
       <c r="D12" s="248"/>
       <c r="E12" s="248"/>
       <c r="F12" s="248"/>
@@ -7200,7 +7187,7 @@
       <c r="Y12" s="248"/>
       <c r="Z12" s="25"/>
     </row>
-    <row r="13" spans="3:26" ht="12.95" customHeight="1">
+    <row r="13" spans="3:26" ht="12.9" customHeight="1">
       <c r="D13" s="248"/>
       <c r="E13" s="248"/>
       <c r="F13" s="248"/>
@@ -7225,7 +7212,7 @@
       <c r="Y13" s="55"/>
       <c r="Z13" s="31"/>
     </row>
-    <row r="14" spans="3:26" ht="12.95" customHeight="1"/>
+    <row r="14" spans="3:26" ht="12.9" customHeight="1"/>
     <row r="15" spans="3:26" ht="15" customHeight="1">
       <c r="C15" s="21" t="s">
         <v>4</v>
@@ -7388,8 +7375,8 @@
       <c r="Y20" s="245"/>
       <c r="Z20" s="245"/>
     </row>
-    <row r="21" spans="1:26" ht="12.95" customHeight="1"/>
-    <row r="22" spans="1:26" ht="12.95" customHeight="1"/>
+    <row r="21" spans="1:26" ht="12.9" customHeight="1"/>
+    <row r="22" spans="1:26" ht="12.9" customHeight="1"/>
     <row r="23" spans="1:26" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="56"/>
       <c r="C23" s="64" t="s">
@@ -7420,7 +7407,7 @@
       <c r="T24" s="31"/>
       <c r="U24" s="31"/>
     </row>
-    <row r="25" spans="1:26" ht="9.9499999999999993" customHeight="1">
+    <row r="25" spans="1:26" ht="9.9" customHeight="1">
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
@@ -7495,7 +7482,7 @@
       <c r="Y27" s="249"/>
       <c r="Z27" s="249"/>
     </row>
-    <row r="28" spans="1:26" ht="9.9499999999999993" customHeight="1"/>
+    <row r="28" spans="1:26" ht="9.9" customHeight="1"/>
     <row r="29" spans="1:26" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="56"/>
       <c r="C29" s="19" t="s">
@@ -7582,7 +7569,7 @@
       <c r="Y32" s="249"/>
       <c r="Z32" s="249"/>
     </row>
-    <row r="33" spans="1:27" ht="9.9499999999999993" customHeight="1"/>
+    <row r="33" spans="1:27" ht="9.9" customHeight="1"/>
     <row r="34" spans="1:27" s="58" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="57"/>
       <c r="C34" s="68" t="s">
@@ -7668,14 +7655,14 @@
       <c r="Y36" s="281"/>
       <c r="Z36" s="281"/>
     </row>
-    <row r="37" spans="1:27" ht="9.9499999999999993" customHeight="1"/>
+    <row r="37" spans="1:27" ht="9.9" customHeight="1"/>
     <row r="38" spans="1:27" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="56"/>
       <c r="C38" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="9.9499999999999993" customHeight="1"/>
+    <row r="39" spans="1:27" ht="9.9" customHeight="1"/>
     <row r="40" spans="1:27" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="56"/>
       <c r="D40" s="240" t="s">
@@ -7774,7 +7761,7 @@
       <c r="Y42" s="242"/>
       <c r="Z42" s="242"/>
     </row>
-    <row r="43" spans="1:27" ht="9.9499999999999993" customHeight="1"/>
+    <row r="43" spans="1:27" ht="9.9" customHeight="1"/>
     <row r="44" spans="1:27" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="56"/>
       <c r="C44" s="19" t="s">
@@ -7876,7 +7863,7 @@
     <row r="49" spans="1:23" s="58" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="57"/>
       <c r="C49" s="58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1">
@@ -10989,7 +10976,7 @@
       <c r="W183" s="230"/>
       <c r="X183" s="231"/>
     </row>
-    <row r="184" spans="5:24" ht="12.95" customHeight="1">
+    <row r="184" spans="5:24" ht="12.9" customHeight="1">
       <c r="E184" s="276"/>
       <c r="F184" s="277"/>
       <c r="G184" s="277"/>
@@ -11023,7 +11010,7 @@
       <c r="W184" s="230"/>
       <c r="X184" s="231"/>
     </row>
-    <row r="185" spans="5:24" ht="12.95" customHeight="1">
+    <row r="185" spans="5:24" ht="12.9" customHeight="1">
       <c r="E185" s="273" t="str">
         <f>DataSheet!F136</f>
         <v>10 A</v>
@@ -11060,7 +11047,7 @@
       <c r="W185" s="230"/>
       <c r="X185" s="231"/>
     </row>
-    <row r="186" spans="5:24" ht="12.95" customHeight="1">
+    <row r="186" spans="5:24" ht="12.9" customHeight="1">
       <c r="E186" s="276"/>
       <c r="F186" s="277"/>
       <c r="G186" s="277"/>
@@ -11094,22 +11081,22 @@
       <c r="W186" s="230"/>
       <c r="X186" s="231"/>
     </row>
-    <row r="187" spans="5:24" ht="12.95" customHeight="1"/>
+    <row r="187" spans="5:24" ht="12.9" customHeight="1"/>
     <row r="188" spans="5:24" ht="15" customHeight="1"/>
     <row r="189" spans="5:24" ht="15" customHeight="1"/>
-    <row r="193" ht="12.95" customHeight="1"/>
-    <row r="194" ht="12.95" customHeight="1"/>
-    <row r="195" ht="12.95" customHeight="1"/>
+    <row r="193" ht="12.9" customHeight="1"/>
+    <row r="194" ht="12.9" customHeight="1"/>
+    <row r="195" ht="12.9" customHeight="1"/>
     <row r="196" ht="15" customHeight="1"/>
     <row r="197" ht="15" customHeight="1"/>
     <row r="198" ht="15" customHeight="1"/>
-    <row r="202" ht="12.95" customHeight="1"/>
-    <row r="203" ht="12.95" customHeight="1"/>
-    <row r="204" ht="12.95" customHeight="1"/>
+    <row r="202" ht="12.9" customHeight="1"/>
+    <row r="203" ht="12.9" customHeight="1"/>
+    <row r="204" ht="12.9" customHeight="1"/>
     <row r="205" ht="15" customHeight="1"/>
     <row r="206" ht="15" customHeight="1"/>
-    <row r="211" spans="3:26" ht="12.95" customHeight="1"/>
-    <row r="212" spans="3:26" ht="12.95" customHeight="1"/>
+    <row r="211" spans="3:26" ht="12.9" customHeight="1"/>
+    <row r="212" spans="3:26" ht="12.9" customHeight="1"/>
     <row r="213" spans="3:26" ht="15" customHeight="1">
       <c r="C213" s="227" t="str">
         <f>DataSheet!B140</f>
@@ -11203,7 +11190,7 @@
     <row r="219" spans="3:26" ht="15" customHeight="1"/>
     <row r="220" spans="3:26" ht="15" customHeight="1"/>
     <row r="221" spans="3:26" ht="15" customHeight="1"/>
-    <row r="222" spans="3:26" ht="12.95" customHeight="1"/>
+    <row r="222" spans="3:26" ht="12.9" customHeight="1"/>
     <row r="240" ht="15" customHeight="1"/>
     <row r="241" ht="15" customHeight="1"/>
     <row r="242" ht="15" customHeight="1"/>
@@ -11588,31 +11575,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:DE187"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="123" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" style="123" customWidth="1"/>
     <col min="2" max="52" width="2" style="127" customWidth="1"/>
     <col min="53" max="74" width="2" style="123" customWidth="1"/>
     <col min="75" max="75" width="2" style="127" customWidth="1"/>
-    <col min="76" max="80" width="10.7109375" style="127" customWidth="1"/>
+    <col min="76" max="80" width="10.6640625" style="127" customWidth="1"/>
     <col min="81" max="81" width="2" style="127" customWidth="1"/>
-    <col min="82" max="86" width="10.7109375" style="127" customWidth="1"/>
+    <col min="82" max="86" width="10.6640625" style="127" customWidth="1"/>
     <col min="87" max="87" width="2" style="127" customWidth="1"/>
-    <col min="88" max="92" width="10.7109375" style="127" customWidth="1"/>
+    <col min="88" max="92" width="10.6640625" style="127" customWidth="1"/>
     <col min="93" max="93" width="2" style="127" customWidth="1"/>
-    <col min="94" max="98" width="10.7109375" style="127" customWidth="1"/>
+    <col min="94" max="98" width="10.6640625" style="127" customWidth="1"/>
     <col min="99" max="99" width="2" style="127" customWidth="1"/>
-    <col min="100" max="102" width="20.7109375" style="127" customWidth="1"/>
-    <col min="103" max="103" width="15.7109375" style="127" customWidth="1"/>
-    <col min="104" max="104" width="5.7109375" style="127" customWidth="1"/>
+    <col min="100" max="102" width="20.6640625" style="127" customWidth="1"/>
+    <col min="103" max="103" width="15.6640625" style="127" customWidth="1"/>
+    <col min="104" max="104" width="5.6640625" style="127" customWidth="1"/>
     <col min="105" max="105" width="2" style="127" customWidth="1"/>
-    <col min="106" max="109" width="10.7109375" style="127" customWidth="1"/>
-    <col min="110" max="16384" width="9.140625" style="127"/>
+    <col min="106" max="109" width="10.6640625" style="127" customWidth="1"/>
+    <col min="110" max="16384" width="9.109375" style="127"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:74" ht="15">
+    <row r="2" spans="1:74" ht="14.4">
       <c r="B2" s="124"/>
       <c r="C2" s="125"/>
       <c r="D2" s="125"/>
@@ -11665,7 +11652,7 @@
       <c r="AY2" s="125"/>
       <c r="AZ2" s="126"/>
     </row>
-    <row r="3" spans="1:74" ht="15">
+    <row r="3" spans="1:74" ht="14.4">
       <c r="B3" s="128"/>
       <c r="C3" s="129"/>
       <c r="D3" s="129"/>
@@ -11718,7 +11705,7 @@
       <c r="AY3" s="129"/>
       <c r="AZ3" s="130"/>
     </row>
-    <row r="4" spans="1:74" ht="15">
+    <row r="4" spans="1:74" ht="14.4">
       <c r="B4" s="128"/>
       <c r="C4" s="129"/>
       <c r="D4" s="129"/>
@@ -11771,7 +11758,7 @@
       <c r="AY4" s="129"/>
       <c r="AZ4" s="130"/>
     </row>
-    <row r="5" spans="1:74" ht="18.75">
+    <row r="5" spans="1:74" ht="17.399999999999999">
       <c r="B5" s="132" t="s">
         <v>30</v>
       </c>
@@ -13235,7 +13222,7 @@
       <c r="BU23" s="136"/>
       <c r="BV23" s="136"/>
     </row>
-    <row r="24" spans="1:74" s="143" customFormat="1" ht="13.5" thickBot="1">
+    <row r="24" spans="1:74" s="143" customFormat="1" ht="14.4" thickBot="1">
       <c r="A24" s="136"/>
       <c r="B24" s="381" t="s">
         <v>47</v>
@@ -13783,7 +13770,7 @@
       <c r="BU30" s="136"/>
       <c r="BV30" s="136"/>
     </row>
-    <row r="31" spans="1:74" s="143" customFormat="1" ht="13.5" thickBot="1">
+    <row r="31" spans="1:74" s="143" customFormat="1" ht="14.4" thickBot="1">
       <c r="A31" s="136"/>
       <c r="B31" s="381" t="s">
         <v>53</v>
@@ -13861,7 +13848,7 @@
       <c r="BU31" s="136"/>
       <c r="BV31" s="136"/>
     </row>
-    <row r="32" spans="1:74" s="143" customFormat="1" ht="12.75">
+    <row r="32" spans="1:74" s="143" customFormat="1" ht="13.8">
       <c r="A32" s="136"/>
       <c r="B32" s="397" t="s">
         <v>18</v>
@@ -13945,7 +13932,7 @@
       <c r="BU32" s="136"/>
       <c r="BV32" s="136"/>
     </row>
-    <row r="33" spans="1:74" s="143" customFormat="1" ht="13.5">
+    <row r="33" spans="1:74" s="143" customFormat="1" ht="13.2">
       <c r="A33" s="136"/>
       <c r="B33" s="357"/>
       <c r="C33" s="355"/>
@@ -14021,7 +14008,7 @@
       <c r="BU33" s="136"/>
       <c r="BV33" s="136"/>
     </row>
-    <row r="34" spans="1:74" s="143" customFormat="1" ht="14.25" thickBot="1">
+    <row r="34" spans="1:74" s="143" customFormat="1" ht="13.8" thickBot="1">
       <c r="A34" s="136"/>
       <c r="B34" s="352"/>
       <c r="C34" s="353"/>
@@ -14097,7 +14084,7 @@
       <c r="BU34" s="136"/>
       <c r="BV34" s="136"/>
     </row>
-    <row r="35" spans="1:74" s="143" customFormat="1" ht="13.5" thickBot="1">
+    <row r="35" spans="1:74" s="143" customFormat="1" ht="14.4" thickBot="1">
       <c r="A35" s="136"/>
       <c r="B35" s="336" t="s">
         <v>54</v>
@@ -14175,7 +14162,7 @@
       <c r="BU35" s="136"/>
       <c r="BV35" s="136"/>
     </row>
-    <row r="36" spans="1:74" s="143" customFormat="1" ht="12.75">
+    <row r="36" spans="1:74" s="143" customFormat="1" ht="13.8">
       <c r="A36" s="136"/>
       <c r="B36" s="397" t="s">
         <v>18</v>
@@ -14259,7 +14246,7 @@
       <c r="BU36" s="136"/>
       <c r="BV36" s="136"/>
     </row>
-    <row r="37" spans="1:74" s="143" customFormat="1" ht="12.75">
+    <row r="37" spans="1:74" s="143" customFormat="1" ht="13.8">
       <c r="A37" s="136"/>
       <c r="B37" s="444"/>
       <c r="C37" s="344"/>
@@ -14335,7 +14322,7 @@
       <c r="BU37" s="136"/>
       <c r="BV37" s="136"/>
     </row>
-    <row r="38" spans="1:74" s="143" customFormat="1" ht="13.5" thickBot="1">
+    <row r="38" spans="1:74" s="143" customFormat="1" ht="14.4" thickBot="1">
       <c r="A38" s="136"/>
       <c r="B38" s="448"/>
       <c r="C38" s="344"/>
@@ -14573,7 +14560,7 @@
       <c r="BU40" s="136"/>
       <c r="BV40" s="136"/>
     </row>
-    <row r="41" spans="1:74" s="143" customFormat="1" ht="15">
+    <row r="41" spans="1:74" s="143" customFormat="1" ht="15.6">
       <c r="A41" s="136"/>
       <c r="B41" s="137"/>
       <c r="C41" s="154"/>
@@ -14898,8 +14885,8 @@
     <row r="45" spans="1:74" s="143" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="136"/>
       <c r="B45" s="137"/>
-      <c r="C45" s="340" t="s">
-        <v>160</v>
+      <c r="C45" s="339" t="s">
+        <v>56</v>
       </c>
       <c r="D45" s="340"/>
       <c r="E45" s="340"/>
@@ -15055,7 +15042,7 @@
       <c r="BU46" s="136"/>
       <c r="BV46" s="136"/>
     </row>
-    <row r="47" spans="1:74" s="143" customFormat="1" ht="12.75">
+    <row r="47" spans="1:74" s="143" customFormat="1" ht="13.8">
       <c r="A47" s="136"/>
       <c r="B47" s="137"/>
       <c r="C47" s="340" t="s">
@@ -15291,7 +15278,7 @@
       <c r="BU49" s="136"/>
       <c r="BV49" s="136"/>
     </row>
-    <row r="50" spans="1:109" s="143" customFormat="1" ht="13.5" thickBot="1">
+    <row r="50" spans="1:109" s="143" customFormat="1" ht="14.4" thickBot="1">
       <c r="A50" s="136"/>
       <c r="B50" s="440" t="s">
         <v>67</v>
@@ -15369,7 +15356,7 @@
       <c r="BU50" s="136"/>
       <c r="BV50" s="136"/>
     </row>
-    <row r="51" spans="1:109" s="143" customFormat="1" ht="12.75" thickBot="1">
+    <row r="51" spans="1:109" s="143" customFormat="1" ht="12.6" thickBot="1">
       <c r="A51" s="136"/>
       <c r="B51" s="166"/>
       <c r="C51" s="167"/>
@@ -19503,7 +19490,7 @@
         <v>V</v>
       </c>
     </row>
-    <row r="72" spans="1:109" s="143" customFormat="1" ht="14.25" thickBot="1">
+    <row r="72" spans="1:109" s="143" customFormat="1" ht="13.8" thickBot="1">
       <c r="A72" s="136"/>
       <c r="B72" s="166"/>
       <c r="C72" s="167"/>
@@ -24729,7 +24716,7 @@
         <v>V</v>
       </c>
     </row>
-    <row r="98" spans="1:109" s="143" customFormat="1" ht="14.25" thickBot="1">
+    <row r="98" spans="1:109" s="143" customFormat="1" ht="13.8" thickBot="1">
       <c r="A98" s="136"/>
       <c r="B98" s="166"/>
       <c r="C98" s="167"/>
@@ -32348,7 +32335,7 @@
       <c r="BV138" s="136"/>
       <c r="BY138" s="217"/>
     </row>
-    <row r="139" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="139" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A139" s="136"/>
       <c r="B139" s="193" t="s">
         <v>104</v>
@@ -32426,7 +32413,7 @@
       <c r="BU139" s="136"/>
       <c r="BV139" s="136"/>
     </row>
-    <row r="140" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="140" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A140" s="136"/>
       <c r="B140" s="434" t="s">
         <v>158</v>
@@ -32507,7 +32494,7 @@
       <c r="BU140" s="136"/>
       <c r="BV140" s="136"/>
     </row>
-    <row r="141" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="141" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A141" s="136"/>
       <c r="B141" s="427" t="s">
         <v>105</v>
@@ -32589,7 +32576,7 @@
       <c r="BU141" s="136"/>
       <c r="BV141" s="136"/>
     </row>
-    <row r="142" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="142" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A142" s="136"/>
       <c r="B142" s="197" t="s">
         <v>108</v>
@@ -32667,7 +32654,7 @@
       <c r="BU142" s="136"/>
       <c r="BV142" s="136"/>
     </row>
-    <row r="143" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="143" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A143" s="136"/>
       <c r="B143" s="412" t="s">
         <v>133</v>
@@ -32745,7 +32732,7 @@
       <c r="BU143" s="136"/>
       <c r="BV143" s="136"/>
     </row>
-    <row r="144" spans="1:109" s="143" customFormat="1" ht="13.5">
+    <row r="144" spans="1:109" s="143" customFormat="1" ht="13.2">
       <c r="A144" s="136"/>
       <c r="B144" s="427" t="s">
         <v>155</v>
@@ -32827,7 +32814,7 @@
       <c r="BU144" s="136"/>
       <c r="BV144" s="136"/>
     </row>
-    <row r="145" spans="1:105" s="143" customFormat="1" ht="13.5">
+    <row r="145" spans="1:105" s="143" customFormat="1" ht="13.2">
       <c r="A145" s="136"/>
       <c r="B145" s="193" t="s">
         <v>109</v>
@@ -32987,7 +32974,7 @@
       <c r="BU146" s="136"/>
       <c r="BV146" s="136"/>
     </row>
-    <row r="147" spans="1:105" s="143" customFormat="1" ht="14.25" thickBot="1">
+    <row r="147" spans="1:105" s="143" customFormat="1" ht="13.8" thickBot="1">
       <c r="A147" s="136"/>
       <c r="B147" s="421" t="s">
         <v>105</v>
@@ -33069,7 +33056,7 @@
       <c r="BU147" s="136"/>
       <c r="BV147" s="136"/>
     </row>
-    <row r="148" spans="1:105" s="201" customFormat="1" ht="15" hidden="1">
+    <row r="148" spans="1:105" s="201" customFormat="1" ht="14.4" hidden="1">
       <c r="A148" s="200"/>
       <c r="B148" s="127"/>
       <c r="C148" s="127"/>
@@ -33176,10 +33163,10 @@
       <c r="CZ148" s="127"/>
       <c r="DA148" s="127"/>
     </row>
-    <row r="149" spans="1:105" ht="15" hidden="1"/>
-    <row r="150" spans="1:105" ht="15" hidden="1"/>
-    <row r="151" spans="1:105" ht="15" hidden="1"/>
-    <row r="152" spans="1:105" ht="15" hidden="1"/>
+    <row r="149" spans="1:105" ht="14.4" hidden="1"/>
+    <row r="150" spans="1:105" ht="14.4" hidden="1"/>
+    <row r="151" spans="1:105" ht="14.4" hidden="1"/>
+    <row r="152" spans="1:105" ht="14.4" hidden="1"/>
     <row r="153" spans="1:105" ht="15" hidden="1" customHeight="1"/>
     <row r="154" spans="1:105" ht="15" hidden="1" customHeight="1"/>
     <row r="155" spans="1:105" ht="15" hidden="1" customHeight="1"/>
@@ -34511,7 +34498,7 @@
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P77:R79 L76:AV76">
+  <conditionalFormatting sqref="L76:AV76 P77:R79">
     <cfRule type="expression" dxfId="112" priority="223">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
@@ -34536,7 +34523,7 @@
       <formula>$BQ$90="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P127:R129 L126:AV126">
+  <conditionalFormatting sqref="L126:AV126 P127:R129">
     <cfRule type="expression" dxfId="107" priority="67">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
@@ -34891,7 +34878,7 @@
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P83:R83 X79:AV79 X83:AV83">
+  <conditionalFormatting sqref="X79:AV79 P83:R83 X83:AV83">
     <cfRule type="expression" dxfId="36" priority="420">
       <formula>$BQ$83="FAIL"</formula>
     </cfRule>
@@ -34926,7 +34913,7 @@
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM120:AV121 X117:AV117">
+  <conditionalFormatting sqref="X117:AV117 AM120:AV121">
     <cfRule type="expression" dxfId="29" priority="396">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
@@ -34960,11 +34947,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ76:BU97">
-    <cfRule type="containsText" dxfId="22" priority="140" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="22" priority="141" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",BQ76)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="21" priority="140" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ76)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="21" priority="141" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",BQ76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ102:BU108">
@@ -34976,19 +34963,19 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ113:BU121">
-    <cfRule type="containsText" dxfId="18" priority="104" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="18" priority="105" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",BQ113)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="17" priority="104" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ113)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="105" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",BQ113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ126:BU137">
-    <cfRule type="containsText" dxfId="16" priority="62" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="16" priority="63" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",BQ126)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="62" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ126)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="63" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",BQ126)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -35003,12 +34990,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Y75"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
     <col min="3" max="3" width="7" customWidth="1"/>
   </cols>
   <sheetData>
@@ -40283,11 +40270,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="204"/>
+    <col min="1" max="16384" width="9.109375" style="204"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ASCal/template.xlsx
+++ b/ASCal/template.xlsx
@@ -3369,7 +3369,7 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 5" xfId="5"/>
   </cellStyles>
-  <dxfs count="142">
+  <dxfs count="144">
     <dxf>
       <fill>
         <patternFill>
@@ -3472,6 +3472,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8053,28 +8073,28 @@
       <c r="H70" s="238"/>
       <c r="I70" s="238" t="str">
         <f>CONCATENATE(DataSheet!L55," ",DataSheet!P55)</f>
-        <v xml:space="preserve"> mV</v>
+        <v>60 mV</v>
       </c>
       <c r="J70" s="238"/>
       <c r="K70" s="238"/>
       <c r="L70" s="238"/>
-      <c r="M70" s="238" t="e">
+      <c r="M70" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AM55,"0.0")," ",DataSheet!P55)</f>
-        <v>#DIV/0!</v>
+        <v>60.0 mV</v>
       </c>
       <c r="N70" s="238"/>
       <c r="O70" s="238"/>
       <c r="P70" s="238"/>
-      <c r="Q70" s="238" t="e">
+      <c r="Q70" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AR55,"0.0")," ",DataSheet!P55)</f>
-        <v>#DIV/0!</v>
+        <v>0.0 mV</v>
       </c>
       <c r="R70" s="238"/>
       <c r="S70" s="238"/>
       <c r="T70" s="238"/>
-      <c r="U70" s="238" t="e">
+      <c r="U70" s="238" t="str">
         <f>CONCATENATE(," ",TEXT(DataSheet!DD55,"0.000")," ",DataSheet!CZ55)</f>
-        <v>#DIV/0!</v>
+        <v xml:space="preserve"> 0.058 mV</v>
       </c>
       <c r="V70" s="238"/>
       <c r="W70" s="238"/>
@@ -8095,21 +8115,21 @@
       <c r="L71" s="238"/>
       <c r="M71" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AM56,"0.0")," ",DataSheet!P56)</f>
-        <v>40.0 mV</v>
+        <v>540.0 mV</v>
       </c>
       <c r="N71" s="238"/>
       <c r="O71" s="238"/>
       <c r="P71" s="238"/>
       <c r="Q71" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AR56,"0.0")," ",DataSheet!P56)</f>
-        <v>-500.0 mV</v>
+        <v>0.0 mV</v>
       </c>
       <c r="R71" s="238"/>
       <c r="S71" s="238"/>
       <c r="T71" s="238"/>
       <c r="U71" s="238" t="str">
         <f>CONCATENATE(," ",TEXT(DataSheet!DD56,"0.000")," ",DataSheet!CZ56)</f>
-        <v xml:space="preserve"> 80.000 mV</v>
+        <v xml:space="preserve"> 0.058 mV</v>
       </c>
       <c r="V71" s="238"/>
       <c r="W71" s="238"/>
@@ -8916,14 +8936,14 @@
       <c r="L96" s="257"/>
       <c r="M96" s="257" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AM107,"0.000")," ",DataSheet!P107)</f>
-        <v>5.400 MΩ</v>
+        <v>540.000 MΩ</v>
       </c>
       <c r="N96" s="257"/>
       <c r="O96" s="257"/>
       <c r="P96" s="257"/>
       <c r="Q96" s="257" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AR107,"0.000")," ",DataSheet!P107)</f>
-        <v>0.000 MΩ</v>
+        <v>534.600 MΩ</v>
       </c>
       <c r="R96" s="257"/>
       <c r="S96" s="257"/>
@@ -9307,14 +9327,14 @@
       <c r="L122" s="238"/>
       <c r="M122" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AM76,"0.0")," ",DataSheet!P76)</f>
-        <v>59.4 mV</v>
+        <v>60.3 mV</v>
       </c>
       <c r="N122" s="238"/>
       <c r="O122" s="238"/>
       <c r="P122" s="238"/>
       <c r="Q122" s="238" t="str">
         <f>CONCATENATE(TEXT(DataSheet!AR76,"0.0")," ",DataSheet!P76)</f>
-        <v>-0.6 mV</v>
+        <v>0.3 mV</v>
       </c>
       <c r="R122" s="238"/>
       <c r="S122" s="238"/>
@@ -15907,7 +15927,9 @@
       <c r="I55" s="320"/>
       <c r="J55" s="320"/>
       <c r="K55" s="321"/>
-      <c r="L55" s="297"/>
+      <c r="L55" s="297">
+        <v>60</v>
+      </c>
       <c r="M55" s="298"/>
       <c r="N55" s="298"/>
       <c r="O55" s="298"/>
@@ -15921,32 +15943,38 @@
       <c r="U55" s="301"/>
       <c r="V55" s="301"/>
       <c r="W55" s="301"/>
-      <c r="X55" s="291"/>
+      <c r="X55" s="291">
+        <v>60</v>
+      </c>
       <c r="Y55" s="291"/>
       <c r="Z55" s="291"/>
       <c r="AA55" s="291"/>
       <c r="AB55" s="291"/>
-      <c r="AC55" s="291"/>
+      <c r="AC55" s="291">
+        <v>60</v>
+      </c>
       <c r="AD55" s="291"/>
       <c r="AE55" s="291"/>
       <c r="AF55" s="291"/>
       <c r="AG55" s="291"/>
-      <c r="AH55" s="291"/>
+      <c r="AH55" s="291">
+        <v>60</v>
+      </c>
       <c r="AI55" s="291"/>
       <c r="AJ55" s="291"/>
       <c r="AK55" s="291"/>
       <c r="AL55" s="291"/>
-      <c r="AM55" s="291" t="e">
+      <c r="AM55" s="291">
         <f t="shared" ref="AM55:AM68" si="0">AVERAGE(X55:AL55)</f>
-        <v>#DIV/0!</v>
+        <v>60</v>
       </c>
       <c r="AN55" s="291"/>
       <c r="AO55" s="291"/>
       <c r="AP55" s="291"/>
       <c r="AQ55" s="291"/>
-      <c r="AR55" s="291" t="e">
+      <c r="AR55" s="291">
         <f>AM55-L55</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="AS55" s="291"/>
       <c r="AT55" s="291"/>
@@ -15957,22 +15985,34 @@
       <c r="AY55" s="139"/>
       <c r="AZ55" s="172"/>
       <c r="BA55" s="173"/>
-      <c r="BB55" s="306"/>
+      <c r="BB55" s="306">
+        <f>ABS(AM55*0.1%)+(1*CK55)</f>
+        <v>0.16</v>
+      </c>
       <c r="BC55" s="306"/>
       <c r="BD55" s="306"/>
       <c r="BE55" s="306"/>
       <c r="BF55" s="306"/>
-      <c r="BG55" s="306"/>
+      <c r="BG55" s="306">
+        <f>L55+BB55</f>
+        <v>60.16</v>
+      </c>
       <c r="BH55" s="306"/>
       <c r="BI55" s="306"/>
       <c r="BJ55" s="306"/>
       <c r="BK55" s="306"/>
-      <c r="BL55" s="306"/>
+      <c r="BL55" s="306">
+        <f>L55-BB55</f>
+        <v>59.84</v>
+      </c>
       <c r="BM55" s="306"/>
       <c r="BN55" s="306"/>
       <c r="BO55" s="306"/>
       <c r="BP55" s="306"/>
-      <c r="BQ55" s="292"/>
+      <c r="BQ55" s="292" t="str">
+        <f>IF(AND(AM55&lt;=BG55,AM55&gt;=BL55),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
       <c r="BR55" s="292"/>
       <c r="BS55" s="292"/>
       <c r="BT55" s="292"/>
@@ -16037,9 +16077,9 @@
       <c r="CP55" s="70" t="s">
         <v>70</v>
       </c>
-      <c r="CQ55" s="83" t="e">
+      <c r="CQ55" s="83">
         <f>STDEV(X55:AL55)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="CR55" s="71" t="str">
         <f t="shared" ref="CR55:CR68" si="2">P55</f>
@@ -16049,26 +16089,26 @@
         <f>SQRT(3)</f>
         <v>1.7320508075688772</v>
       </c>
-      <c r="CT55" s="85" t="e">
+      <c r="CT55" s="85">
         <f>CQ55/CS55</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="CU55" s="8"/>
-      <c r="CV55" s="92" t="e">
+      <c r="CV55" s="92">
         <f>SQRT(SUMSQ(CT55,CN55,CH55,CB55))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="CW55" s="88" t="e">
+        <v>2.8870080677638112E-2</v>
+      </c>
+      <c r="CW55" s="88">
         <f>(CV55^4)/(((CT55^4)/2)+((CN55^4)/200)+((CH55^4)/200)+((CB55^4)/200))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="CX55" s="93" t="e">
+        <v>200.07114799774902</v>
+      </c>
+      <c r="CX55" s="93">
         <f>ROUND(TINV(0.05,CW55),0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="CY55" s="103" t="e">
+        <v>2</v>
+      </c>
+      <c r="CY55" s="103">
         <f>(CV55*CX55)</f>
-        <v>#DIV/0!</v>
+        <v>5.7740161355276223E-2</v>
       </c>
       <c r="CZ55" s="104" t="str">
         <f t="shared" ref="CZ55:CZ68" si="3">P55</f>
@@ -16082,9 +16122,9 @@
         <f>CZ55</f>
         <v>mV</v>
       </c>
-      <c r="DD55" s="220" t="e">
+      <c r="DD55" s="220">
         <f>MAX(DB55,CY55)</f>
-        <v>#DIV/0!</v>
+        <v>5.7740161355276223E-2</v>
       </c>
       <c r="DE55" s="178" t="s">
         <v>161</v>
@@ -16122,21 +16162,21 @@
       <c r="V56" s="301"/>
       <c r="W56" s="301"/>
       <c r="X56" s="307">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="Y56" s="308"/>
       <c r="Z56" s="308"/>
       <c r="AA56" s="308"/>
       <c r="AB56" s="308"/>
       <c r="AC56" s="307">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="AD56" s="308"/>
       <c r="AE56" s="308"/>
       <c r="AF56" s="308"/>
       <c r="AG56" s="308"/>
       <c r="AH56" s="307">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="AI56" s="308"/>
       <c r="AJ56" s="308"/>
@@ -16144,7 +16184,7 @@
       <c r="AL56" s="308"/>
       <c r="AM56" s="307">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="AN56" s="308"/>
       <c r="AO56" s="308"/>
@@ -16152,7 +16192,7 @@
       <c r="AQ56" s="309"/>
       <c r="AR56" s="307">
         <f t="shared" ref="AR56:AR68" si="4">AM56-L56</f>
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="AS56" s="308"/>
       <c r="AT56" s="308"/>
@@ -16165,7 +16205,7 @@
       <c r="BA56" s="173"/>
       <c r="BB56" s="306">
         <f t="shared" ref="BB56:BB57" si="5">ABS(AM56*0.1%)+(1*CK56)</f>
-        <v>0.14000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="BC56" s="306"/>
       <c r="BD56" s="306"/>
@@ -16173,7 +16213,7 @@
       <c r="BF56" s="306"/>
       <c r="BG56" s="291">
         <f t="shared" ref="BG56:BG68" si="6">L56+BB56</f>
-        <v>540.14</v>
+        <v>540.64</v>
       </c>
       <c r="BH56" s="291"/>
       <c r="BI56" s="291"/>
@@ -16181,7 +16221,7 @@
       <c r="BK56" s="291"/>
       <c r="BL56" s="291">
         <f t="shared" ref="BL56:BL68" si="7">L56-BB56</f>
-        <v>539.86</v>
+        <v>539.36</v>
       </c>
       <c r="BM56" s="291"/>
       <c r="BN56" s="291"/>
@@ -16189,7 +16229,7 @@
       <c r="BP56" s="291"/>
       <c r="BQ56" s="292" t="str">
         <f t="shared" ref="BQ56:BQ68" si="8">IF(AND(AM56&lt;=BG56,AM56&gt;=BL56),"PASS","FAIL")</f>
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="BR56" s="292"/>
       <c r="BS56" s="292"/>
@@ -16257,7 +16297,7 @@
       </c>
       <c r="CQ56" s="6">
         <f t="shared" ref="CQ56:CQ68" si="16">STDEV(X56:AL56)</f>
-        <v>34.641016151377549</v>
+        <v>0</v>
       </c>
       <c r="CR56" s="1" t="str">
         <f t="shared" si="2"/>
@@ -16269,24 +16309,24 @@
       </c>
       <c r="CT56" s="86">
         <f t="shared" ref="CT56:CT68" si="18">CQ56/CS56</f>
-        <v>20.000000000000004</v>
+        <v>0</v>
       </c>
       <c r="CU56" s="8"/>
       <c r="CV56" s="94">
         <f t="shared" ref="CV56:CV68" si="19">SQRT(SUMSQ(CT56,CN56,CH56,CB56))</f>
-        <v>20.000020860884955</v>
+        <v>2.8886603007853544E-2</v>
       </c>
       <c r="CW56" s="5">
         <f t="shared" ref="CW56:CW68" si="20">(CV56^4)/(((CT56^4)/2)+((CN56^4)/200)+((CH56^4)/200)+((CB56^4)/200))</f>
-        <v>2.0000083443669494</v>
+        <v>200.52919907372751</v>
       </c>
       <c r="CX56" s="95">
         <f t="shared" ref="CX56:CX57" si="21">ROUND(TINV(0.05,CW56),0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CY56" s="105">
         <f t="shared" ref="CY56:CY58" si="22">(CV56*CX56)</f>
-        <v>80.000083443539822</v>
+        <v>5.7773206015707089E-2</v>
       </c>
       <c r="CZ56" s="106" t="str">
         <f t="shared" si="3"/>
@@ -16302,7 +16342,7 @@
       </c>
       <c r="DD56" s="220">
         <f t="shared" ref="DD56:DD71" si="24">MAX(DB56,CY56)</f>
-        <v>80.000083443539822</v>
+        <v>5.7773206015707089E-2</v>
       </c>
       <c r="DE56" s="178" t="str">
         <f t="shared" ref="DE56:DE68" si="25">DC56</f>
@@ -20084,14 +20124,14 @@
       <c r="AA76" s="308"/>
       <c r="AB76" s="309"/>
       <c r="AC76" s="307">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="AD76" s="308"/>
       <c r="AE76" s="308"/>
       <c r="AF76" s="308"/>
       <c r="AG76" s="309"/>
       <c r="AH76" s="307">
-        <v>59.1</v>
+        <v>60.9</v>
       </c>
       <c r="AI76" s="308"/>
       <c r="AJ76" s="308"/>
@@ -20099,7 +20139,7 @@
       <c r="AL76" s="309"/>
       <c r="AM76" s="307">
         <f t="shared" ref="AM76:AM79" si="59">AVERAGE(X76:AL76)</f>
-        <v>59.4</v>
+        <v>60.300000000000004</v>
       </c>
       <c r="AN76" s="308"/>
       <c r="AO76" s="308"/>
@@ -20107,7 +20147,7 @@
       <c r="AQ76" s="309"/>
       <c r="AR76" s="291">
         <f t="shared" ref="AR76:AR79" si="60">AM76-L76</f>
-        <v>-0.60000000000000142</v>
+        <v>0.30000000000000426</v>
       </c>
       <c r="AS76" s="291"/>
       <c r="AT76" s="291"/>
@@ -20120,7 +20160,7 @@
       <c r="BA76" s="173"/>
       <c r="BB76" s="329">
         <f>(AM76*0.7%)+(4*CK76)</f>
-        <v>0.81579999999999997</v>
+        <v>0.82210000000000005</v>
       </c>
       <c r="BC76" s="329"/>
       <c r="BD76" s="329"/>
@@ -20128,7 +20168,7 @@
       <c r="BF76" s="329"/>
       <c r="BG76" s="329">
         <f t="shared" ref="BG76:BG79" si="61">L76+BB76</f>
-        <v>60.815800000000003</v>
+        <v>60.822099999999999</v>
       </c>
       <c r="BH76" s="329"/>
       <c r="BI76" s="329"/>
@@ -20136,7 +20176,7 @@
       <c r="BK76" s="329"/>
       <c r="BL76" s="329">
         <f t="shared" ref="BL76:BL79" si="62">L76-BB76</f>
-        <v>59.184199999999997</v>
+        <v>59.177900000000001</v>
       </c>
       <c r="BM76" s="329"/>
       <c r="BN76" s="329"/>
@@ -26537,21 +26577,21 @@
       <c r="V107" s="301"/>
       <c r="W107" s="301"/>
       <c r="X107" s="329">
-        <v>5.4</v>
+        <v>540</v>
       </c>
       <c r="Y107" s="329"/>
       <c r="Z107" s="329"/>
       <c r="AA107" s="329"/>
       <c r="AB107" s="329"/>
       <c r="AC107" s="329">
-        <v>5.4</v>
+        <v>540</v>
       </c>
       <c r="AD107" s="329"/>
       <c r="AE107" s="329"/>
       <c r="AF107" s="329"/>
       <c r="AG107" s="329"/>
       <c r="AH107" s="329">
-        <v>5.4</v>
+        <v>540</v>
       </c>
       <c r="AI107" s="329"/>
       <c r="AJ107" s="329"/>
@@ -26559,7 +26599,7 @@
       <c r="AL107" s="329"/>
       <c r="AM107" s="329">
         <f t="shared" ref="AM107" si="169">AVERAGE(X107:AL107)</f>
-        <v>5.4000000000000012</v>
+        <v>540</v>
       </c>
       <c r="AN107" s="329"/>
       <c r="AO107" s="329"/>
@@ -26567,7 +26607,7 @@
       <c r="AQ107" s="329"/>
       <c r="AR107" s="329">
         <f t="shared" ref="AR107" si="170">AM107-L107</f>
-        <v>0</v>
+        <v>534.6</v>
       </c>
       <c r="AS107" s="329"/>
       <c r="AT107" s="329"/>
@@ -26580,7 +26620,7 @@
       <c r="BA107" s="173"/>
       <c r="BB107" s="291">
         <f>(AM107*0.6%)+(1*CK107)</f>
-        <v>3.3400000000000006E-2</v>
+        <v>3.2410000000000001</v>
       </c>
       <c r="BC107" s="291"/>
       <c r="BD107" s="291"/>
@@ -26588,7 +26628,7 @@
       <c r="BF107" s="291"/>
       <c r="BG107" s="291">
         <f t="shared" ref="BG107" si="171">L107+BB107</f>
-        <v>5.4334000000000007</v>
+        <v>8.641</v>
       </c>
       <c r="BH107" s="291"/>
       <c r="BI107" s="291"/>
@@ -26596,7 +26636,7 @@
       <c r="BK107" s="291"/>
       <c r="BL107" s="291">
         <f t="shared" ref="BL107" si="172">L107-BB107</f>
-        <v>5.3666</v>
+        <v>2.1590000000000003</v>
       </c>
       <c r="BM107" s="291"/>
       <c r="BN107" s="291"/>
@@ -26604,7 +26644,7 @@
       <c r="BP107" s="291"/>
       <c r="BQ107" s="292" t="str">
         <f t="shared" ref="BQ107" si="173">IF(AND(AM107&lt;=BG107,AM107&gt;=BL107),"PASS","FAIL")</f>
-        <v>PASS</v>
+        <v>FAIL</v>
       </c>
       <c r="BR107" s="292"/>
       <c r="BS107" s="292"/>
@@ -26672,7 +26712,7 @@
       </c>
       <c r="CQ107" s="6">
         <f t="shared" ref="CQ107" si="180">STDEV(X107:AL107)</f>
-        <v>1.0877919644084146E-15</v>
+        <v>0</v>
       </c>
       <c r="CR107" s="1" t="str">
         <f t="shared" ref="CR107" si="181">P107</f>
@@ -26684,7 +26724,7 @@
       </c>
       <c r="CT107" s="86">
         <f t="shared" ref="CT107" si="182">CQ107/CS107</f>
-        <v>6.2803698347350997E-16</v>
+        <v>0</v>
       </c>
       <c r="CU107" s="8"/>
       <c r="CV107" s="94">
@@ -34688,628 +34728,636 @@
     <mergeCell ref="S126:W126"/>
   </mergeCells>
   <conditionalFormatting sqref="B140:T140 AK140:AZ140 B143:T143 AK143:AZ143 B146:T146 AK146:AZ147">
-    <cfRule type="notContainsBlanks" dxfId="141" priority="451">
+    <cfRule type="notContainsBlanks" dxfId="143" priority="453">
       <formula>LEN(TRIM(B140))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33:AZ34">
-    <cfRule type="notContainsBlanks" dxfId="140" priority="287">
+    <cfRule type="notContainsBlanks" dxfId="142" priority="289">
       <formula>LEN(TRIM(B33))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L55:L60">
-    <cfRule type="expression" dxfId="139" priority="232">
+    <cfRule type="expression" dxfId="141" priority="234">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L7:N7 AN7:AP7 K9:AA22 AL9:AZ22 AG29:AX29 B37:AZ38 K41:L42 T41:U42 C45:AS48">
-    <cfRule type="notContainsBlanks" dxfId="138" priority="452">
+    <cfRule type="notContainsBlanks" dxfId="140" priority="454">
       <formula>LEN(TRIM(B7))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L62:O65">
-    <cfRule type="expression" dxfId="137" priority="228">
+    <cfRule type="expression" dxfId="139" priority="230">
       <formula>$BQ$61="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L70:O71">
-    <cfRule type="expression" dxfId="136" priority="146">
+    <cfRule type="expression" dxfId="138" priority="148">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L77:O83">
-    <cfRule type="expression" dxfId="135" priority="186">
+    <cfRule type="expression" dxfId="137" priority="188">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L85:O89">
-    <cfRule type="expression" dxfId="134" priority="181">
+    <cfRule type="expression" dxfId="136" priority="183">
       <formula>$BQ$84="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L95:O97">
-    <cfRule type="expression" dxfId="133" priority="134">
+    <cfRule type="expression" dxfId="135" priority="136">
       <formula>$BQ$90="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L113:O117">
-    <cfRule type="expression" dxfId="132" priority="36">
+    <cfRule type="expression" dxfId="134" priority="38">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L127:O133">
-    <cfRule type="expression" dxfId="131" priority="24">
+    <cfRule type="expression" dxfId="133" priority="26">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L61:R61 X61:AV61">
-    <cfRule type="expression" dxfId="130" priority="437">
+    <cfRule type="expression" dxfId="132" priority="439">
       <formula>$BQ$61="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L66:R66">
-    <cfRule type="expression" dxfId="129" priority="429">
+    <cfRule type="expression" dxfId="131" priority="431">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L67:R67">
-    <cfRule type="expression" dxfId="128" priority="428">
+    <cfRule type="expression" dxfId="130" priority="430">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L68:R68">
-    <cfRule type="expression" dxfId="127" priority="427">
+    <cfRule type="expression" dxfId="129" priority="429">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L69:R69">
-    <cfRule type="expression" dxfId="126" priority="150">
+    <cfRule type="expression" dxfId="128" priority="152">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L91:R91 X91:AV91">
-    <cfRule type="expression" dxfId="125" priority="411">
+    <cfRule type="expression" dxfId="127" priority="413">
       <formula>$BQ$91="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L93:R93 X93:AV93">
-    <cfRule type="expression" dxfId="124" priority="409">
+    <cfRule type="expression" dxfId="126" priority="411">
       <formula>$BQ$93="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L102:R102 X102:AV102">
-    <cfRule type="expression" dxfId="123" priority="408">
+    <cfRule type="expression" dxfId="125" priority="410">
       <formula>$BQ$102="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L103:R103 X103:AV103">
-    <cfRule type="expression" dxfId="122" priority="407">
+    <cfRule type="expression" dxfId="124" priority="409">
       <formula>$BQ$103="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L104:R104 X104:AV104">
-    <cfRule type="expression" dxfId="121" priority="406">
+    <cfRule type="expression" dxfId="123" priority="408">
       <formula>$BQ$104="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L105:R105 X105:AV105">
-    <cfRule type="expression" dxfId="120" priority="405">
+    <cfRule type="expression" dxfId="122" priority="407">
       <formula>$BQ$105="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L106:R107">
-    <cfRule type="expression" dxfId="119" priority="157">
+    <cfRule type="expression" dxfId="121" priority="159">
       <formula>$BQ$106="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L108:R108">
-    <cfRule type="expression" dxfId="118" priority="402">
+    <cfRule type="expression" dxfId="120" priority="404">
       <formula>$BQ$108="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L118:R121">
-    <cfRule type="expression" dxfId="117" priority="174">
+    <cfRule type="expression" dxfId="119" priority="176">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L135:R137">
-    <cfRule type="expression" dxfId="116" priority="171">
+    <cfRule type="expression" dxfId="118" priority="173">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P77:R79 L76:AV76">
-    <cfRule type="expression" dxfId="115" priority="226">
+    <cfRule type="expression" dxfId="117" priority="228">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L84:AV84">
-    <cfRule type="expression" dxfId="114" priority="422">
+    <cfRule type="expression" dxfId="116" priority="424">
       <formula>$BQ$84="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L90:AV90">
-    <cfRule type="expression" dxfId="113" priority="412">
+    <cfRule type="expression" dxfId="115" priority="414">
       <formula>$BQ$90="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L92:AV92">
-    <cfRule type="expression" dxfId="112" priority="410">
+    <cfRule type="expression" dxfId="114" priority="412">
       <formula>$BQ$92="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L94:AV94">
-    <cfRule type="expression" dxfId="111" priority="142">
+    <cfRule type="expression" dxfId="113" priority="144">
       <formula>$BQ$90="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P127:R129 L126:AV126">
-    <cfRule type="expression" dxfId="110" priority="70">
+    <cfRule type="expression" dxfId="112" priority="72">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L134:AV134">
-    <cfRule type="expression" dxfId="109" priority="398">
+    <cfRule type="expression" dxfId="111" priority="400">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55 X55:AV55">
-    <cfRule type="expression" dxfId="108" priority="443">
+    <cfRule type="expression" dxfId="110" priority="445">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P56:R56 X56:AV56">
-    <cfRule type="expression" dxfId="107" priority="442">
+    <cfRule type="expression" dxfId="109" priority="444">
       <formula>$BQ$56="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P57:R57 X57:AV57">
-    <cfRule type="expression" dxfId="106" priority="441">
+    <cfRule type="expression" dxfId="108" priority="443">
       <formula>$BQ$57="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:R58 X58:AV58">
-    <cfRule type="expression" dxfId="105" priority="440">
+    <cfRule type="expression" dxfId="107" priority="442">
       <formula>$BQ$58="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59:R59 X59:AV59">
-    <cfRule type="expression" dxfId="104" priority="439">
+    <cfRule type="expression" dxfId="106" priority="441">
       <formula>$BQ$59="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P60:R60 X60:AV60">
-    <cfRule type="expression" dxfId="103" priority="438">
+    <cfRule type="expression" dxfId="105" priority="440">
       <formula>$BQ$60="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62:R62 X62:AV62">
-    <cfRule type="expression" dxfId="102" priority="436">
+    <cfRule type="expression" dxfId="104" priority="438">
       <formula>$BQ$62="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P63:R63 X63:AV63">
-    <cfRule type="expression" dxfId="101" priority="435">
+    <cfRule type="expression" dxfId="103" priority="437">
       <formula>$BQ$63="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P64:R64 X64:AV64">
-    <cfRule type="expression" dxfId="100" priority="434">
+    <cfRule type="expression" dxfId="102" priority="436">
       <formula>$BQ$64="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65:R65 X65:AV65">
-    <cfRule type="expression" dxfId="99" priority="433">
+    <cfRule type="expression" dxfId="101" priority="435">
       <formula>$BQ$65="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P70:R70">
-    <cfRule type="expression" dxfId="98" priority="149">
+    <cfRule type="expression" dxfId="100" priority="151">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P71:R71">
-    <cfRule type="expression" dxfId="97" priority="148">
+    <cfRule type="expression" dxfId="99" priority="150">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P85:R85 X85:AV85">
-    <cfRule type="expression" dxfId="96" priority="421">
+    <cfRule type="expression" dxfId="98" priority="423">
       <formula>$BQ$85="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P87:R87 X87:AV87">
-    <cfRule type="expression" dxfId="95" priority="419">
+    <cfRule type="expression" dxfId="97" priority="421">
       <formula>$BQ$87="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P89:R89 X89:AV89">
-    <cfRule type="expression" dxfId="94" priority="417">
+    <cfRule type="expression" dxfId="96" priority="419">
       <formula>$BQ$89="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P95:R95 X95:AV95">
-    <cfRule type="expression" dxfId="93" priority="141">
+    <cfRule type="expression" dxfId="95" priority="143">
       <formula>$BQ$91="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P97:R97 X97:AV97">
-    <cfRule type="expression" dxfId="92" priority="139">
+    <cfRule type="expression" dxfId="94" priority="141">
       <formula>$BQ$93="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P113:R114">
-    <cfRule type="expression" dxfId="91" priority="109">
+    <cfRule type="expression" dxfId="93" priority="111">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P115:R115">
-    <cfRule type="expression" dxfId="90" priority="132">
+    <cfRule type="expression" dxfId="92" priority="134">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P116:R116">
-    <cfRule type="expression" dxfId="89" priority="131">
+    <cfRule type="expression" dxfId="91" priority="133">
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P117:R117">
-    <cfRule type="expression" dxfId="88" priority="125">
+    <cfRule type="expression" dxfId="90" priority="127">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P132:R132">
-    <cfRule type="expression" dxfId="87" priority="101">
+    <cfRule type="expression" dxfId="89" priority="103">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P133:R133">
-    <cfRule type="expression" dxfId="86" priority="100">
+    <cfRule type="expression" dxfId="88" priority="102">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:AV80">
-    <cfRule type="expression" dxfId="85" priority="426">
+    <cfRule type="expression" dxfId="87" priority="428">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P81:AV81">
-    <cfRule type="expression" dxfId="84" priority="167">
+    <cfRule type="expression" dxfId="86" priority="169">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P82:AV82">
-    <cfRule type="expression" dxfId="83" priority="424">
+    <cfRule type="expression" dxfId="85" priority="426">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P86:AV86">
-    <cfRule type="expression" dxfId="82" priority="420">
+    <cfRule type="expression" dxfId="84" priority="422">
       <formula>$BQ$86="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P88:AV88">
-    <cfRule type="expression" dxfId="81" priority="418">
+    <cfRule type="expression" dxfId="83" priority="420">
       <formula>$BQ$88="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P96:AV96">
-    <cfRule type="expression" dxfId="80" priority="140">
+    <cfRule type="expression" dxfId="82" priority="142">
       <formula>$BQ$92="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P130:AV130">
-    <cfRule type="expression" dxfId="79" priority="103">
+    <cfRule type="expression" dxfId="81" priority="105">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P131:AV131">
-    <cfRule type="expression" dxfId="78" priority="29">
+    <cfRule type="expression" dxfId="80" priority="31">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S79:W79">
-    <cfRule type="expression" dxfId="77" priority="168">
+    <cfRule type="expression" dxfId="79" priority="170">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S83:W83">
+    <cfRule type="expression" dxfId="78" priority="168">
+      <formula>$BQ$81="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S85:W85">
+    <cfRule type="expression" dxfId="77" priority="167">
+      <formula>$BQ$81="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S87:W87">
     <cfRule type="expression" dxfId="76" priority="166">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S85:W85">
+  <conditionalFormatting sqref="S89:W89">
     <cfRule type="expression" dxfId="75" priority="165">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S87:W87">
+  <conditionalFormatting sqref="S91:W91">
     <cfRule type="expression" dxfId="74" priority="164">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S89:W89">
+  <conditionalFormatting sqref="S93:W93">
     <cfRule type="expression" dxfId="73" priority="163">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S91:W91">
-    <cfRule type="expression" dxfId="72" priority="162">
-      <formula>$BQ$81="FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S93:W93">
-    <cfRule type="expression" dxfId="71" priority="161">
-      <formula>$BQ$81="FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="S95:W95">
-    <cfRule type="expression" dxfId="70" priority="138">
+    <cfRule type="expression" dxfId="72" priority="140">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:W97">
-    <cfRule type="expression" dxfId="69" priority="137">
+    <cfRule type="expression" dxfId="71" priority="139">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S128:W128">
-    <cfRule type="expression" dxfId="68" priority="42">
+    <cfRule type="expression" dxfId="70" priority="44">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S129:W129">
-    <cfRule type="expression" dxfId="67" priority="32">
+    <cfRule type="expression" dxfId="69" priority="34">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S132:W132">
-    <cfRule type="expression" dxfId="66" priority="75">
+    <cfRule type="expression" dxfId="68" priority="77">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S133:W133">
+    <cfRule type="expression" dxfId="67" priority="30">
+      <formula>$BQ$135="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S136:W136">
+    <cfRule type="expression" dxfId="66" priority="172">
+      <formula>$BQ$134="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S137:W137">
     <cfRule type="expression" dxfId="65" priority="28">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S136:W136">
-    <cfRule type="expression" dxfId="64" priority="170">
-      <formula>$BQ$134="FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S137:W137">
-    <cfRule type="expression" dxfId="63" priority="26">
-      <formula>$BQ$135="FAIL"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="S77:AV77">
-    <cfRule type="expression" dxfId="62" priority="225">
+    <cfRule type="expression" dxfId="64" priority="227">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S78:AV78">
-    <cfRule type="expression" dxfId="61" priority="224">
+    <cfRule type="expression" dxfId="63" priority="226">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S127:AV127">
-    <cfRule type="expression" dxfId="60" priority="69">
+    <cfRule type="expression" dxfId="62" priority="71">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S135:AV135">
-    <cfRule type="expression" dxfId="59" priority="27">
+    <cfRule type="expression" dxfId="61" priority="29">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X55:AL71">
-    <cfRule type="notContainsBlanks" dxfId="58" priority="156">
+    <cfRule type="notContainsBlanks" dxfId="60" priority="158">
       <formula>LEN(TRIM(X55))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X76:AL97">
-    <cfRule type="notContainsBlanks" dxfId="57" priority="145">
+    <cfRule type="notContainsBlanks" dxfId="59" priority="147">
       <formula>LEN(TRIM(X76))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X79:AL79">
-    <cfRule type="expression" dxfId="56" priority="15">
+    <cfRule type="expression" dxfId="58" priority="17">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X83:AL83">
-    <cfRule type="expression" dxfId="55" priority="13">
+    <cfRule type="expression" dxfId="57" priority="15">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X102:AL108">
-    <cfRule type="notContainsBlanks" dxfId="54" priority="160">
+    <cfRule type="notContainsBlanks" dxfId="56" priority="162">
       <formula>LEN(TRIM(X102))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X113:AL121">
-    <cfRule type="notContainsBlanks" dxfId="53" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="55" priority="13">
       <formula>LEN(TRIM(X113))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X119:AL121">
-    <cfRule type="expression" dxfId="52" priority="9">
+    <cfRule type="expression" dxfId="54" priority="11">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X120:AL121">
-    <cfRule type="expression" dxfId="51" priority="10">
+    <cfRule type="expression" dxfId="53" priority="12">
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X126:AL137">
-    <cfRule type="notContainsBlanks" dxfId="50" priority="71">
+    <cfRule type="notContainsBlanks" dxfId="52" priority="73">
       <formula>LEN(TRIM(X126))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X129:AL129">
-    <cfRule type="expression" dxfId="49" priority="4">
+    <cfRule type="expression" dxfId="51" priority="6">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X133:AL133">
-    <cfRule type="expression" dxfId="48" priority="6">
+    <cfRule type="expression" dxfId="50" priority="8">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X135:AL137">
-    <cfRule type="expression" dxfId="47" priority="5">
+    <cfRule type="expression" dxfId="49" priority="7">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X137:AL137">
-    <cfRule type="expression" dxfId="46" priority="19">
+    <cfRule type="expression" dxfId="48" priority="21">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X66:AV66">
-    <cfRule type="expression" dxfId="45" priority="432">
+    <cfRule type="expression" dxfId="47" priority="434">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X67:AV67">
-    <cfRule type="expression" dxfId="44" priority="431">
+    <cfRule type="expression" dxfId="46" priority="433">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X68:AV68">
-    <cfRule type="expression" dxfId="43" priority="430">
+    <cfRule type="expression" dxfId="45" priority="432">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X69:AV69">
-    <cfRule type="expression" dxfId="42" priority="153">
+    <cfRule type="expression" dxfId="44" priority="155">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X70:AV70">
-    <cfRule type="expression" dxfId="41" priority="152">
+    <cfRule type="expression" dxfId="43" priority="154">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X71:AV71">
-    <cfRule type="expression" dxfId="40" priority="151">
+    <cfRule type="expression" dxfId="42" priority="153">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:R83 X79:AV79 X83:AV83">
-    <cfRule type="expression" dxfId="39" priority="423">
+    <cfRule type="expression" dxfId="41" priority="425">
       <formula>$BQ$83="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X106:AV107">
-    <cfRule type="expression" dxfId="38" priority="404">
+    <cfRule type="expression" dxfId="40" priority="406">
       <formula>$BQ$106="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X108:AV108">
-    <cfRule type="expression" dxfId="37" priority="403">
+    <cfRule type="expression" dxfId="39" priority="405">
       <formula>$BQ$108="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X113:AV113">
-    <cfRule type="expression" dxfId="36" priority="120">
+    <cfRule type="expression" dxfId="38" priority="122">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X114:AV114">
-    <cfRule type="expression" dxfId="35" priority="118">
+    <cfRule type="expression" dxfId="37" priority="120">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X115:AV115 X118:AV118">
-    <cfRule type="expression" dxfId="34" priority="401">
+    <cfRule type="expression" dxfId="36" priority="403">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X116:AV116 X119:AV119">
-    <cfRule type="expression" dxfId="33" priority="400">
+    <cfRule type="expression" dxfId="35" priority="402">
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM120:AV121 X117:AV117">
-    <cfRule type="expression" dxfId="32" priority="399">
+    <cfRule type="expression" dxfId="34" priority="401">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X128:AV128">
-    <cfRule type="expression" dxfId="31" priority="73">
+    <cfRule type="expression" dxfId="33" priority="75">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X129:AV129">
-    <cfRule type="expression" dxfId="30" priority="72">
+    <cfRule type="expression" dxfId="32" priority="74">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X132:AV132 X136:AV136">
-    <cfRule type="expression" dxfId="29" priority="396">
+    <cfRule type="expression" dxfId="31" priority="398">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X133:AV133 X137:AV137">
-    <cfRule type="expression" dxfId="28" priority="395">
+    <cfRule type="expression" dxfId="30" priority="397">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BQ55:BU71">
-    <cfRule type="containsText" dxfId="27" priority="154" operator="containsText" text="PASS">
-      <formula>NOT(ISERROR(SEARCH("PASS",BQ55)))</formula>
+  <conditionalFormatting sqref="BQ56:BU71">
+    <cfRule type="containsText" dxfId="29" priority="156" operator="containsText" text="PASS">
+      <formula>NOT(ISERROR(SEARCH("PASS",BQ56)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="155" operator="containsText" text="FAIL">
-      <formula>NOT(ISERROR(SEARCH("FAIL",BQ55)))</formula>
+    <cfRule type="containsText" dxfId="28" priority="157" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",BQ56)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ76:BU97">
-    <cfRule type="containsText" dxfId="25" priority="144" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="27" priority="146" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="143" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="26" priority="145" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ102:BU108">
-    <cfRule type="containsText" dxfId="23" priority="158" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="25" priority="160" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ102)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="159" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="24" priority="161" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ102)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ113:BU121">
-    <cfRule type="containsText" dxfId="21" priority="108" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="23" priority="110" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ113)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="107" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="22" priority="109" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ126:BU137">
-    <cfRule type="containsText" dxfId="19" priority="66" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="21" priority="68" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ126)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="65" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="20" priority="67" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ126)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X57:AL57">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="19" priority="5">
       <formula>$BQ$56="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X77:AB77">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="18" priority="4">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC77:AL77">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="17" priority="3">
       <formula>$BQ$80="FAIL"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BQ55:BU55">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="PASS">
+      <formula>NOT(ISERROR(SEARCH("PASS",BQ55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="FAIL">
+      <formula>NOT(ISERROR(SEARCH("FAIL",BQ55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -35577,95 +35625,95 @@
       <c r="Y9" s="460"/>
     </row>
     <row r="10" spans="2:25">
-      <c r="B10" s="43" t="e">
+      <c r="B10" s="43">
         <f>DataSheet!AM55</f>
-        <v>#DIV/0!</v>
+        <v>60</v>
       </c>
       <c r="C10" s="44" t="str">
         <f>DataSheet!P55</f>
         <v>mV</v>
       </c>
-      <c r="D10" s="51" t="e">
+      <c r="D10" s="51">
         <f>ABS((B10*0.7%)+(3*DataSheet!CK55))</f>
-        <v>#DIV/0!</v>
+        <v>0.72</v>
       </c>
       <c r="E10" s="35" t="str">
         <f>C10</f>
         <v>mV</v>
       </c>
-      <c r="F10" s="38" t="e">
+      <c r="F10" s="38">
         <f>DataSheet!DD55</f>
-        <v>#DIV/0!</v>
+        <v>5.7740161355276223E-2</v>
       </c>
       <c r="G10" s="35" t="str">
         <f>E10</f>
         <v>mV</v>
       </c>
-      <c r="H10" s="39" t="e">
+      <c r="H10" s="39">
         <f>DataSheet!L55+D10</f>
-        <v>#DIV/0!</v>
+        <v>60.72</v>
       </c>
       <c r="I10" s="35" t="str">
         <f>G10</f>
         <v>mV</v>
       </c>
-      <c r="J10" s="39" t="e">
+      <c r="J10" s="39">
         <f>DataSheet!L55-D10</f>
-        <v>#DIV/0!</v>
+        <v>59.28</v>
       </c>
       <c r="K10" s="35" t="str">
         <f>I10</f>
         <v>mV</v>
       </c>
-      <c r="L10" s="480" t="e">
+      <c r="L10" s="480" t="str">
         <f>IF(AND(B10&lt;=H10,B10&gt;=J10),"PASSED","FAILED")</f>
-        <v>#DIV/0!</v>
+        <v>PASSED</v>
       </c>
       <c r="M10" s="480"/>
-      <c r="N10" s="39" t="e">
+      <c r="N10" s="39">
         <f>F10+B10</f>
-        <v>#DIV/0!</v>
+        <v>60.057740161355277</v>
       </c>
       <c r="O10" s="40" t="str">
         <f>G10</f>
         <v>mV</v>
       </c>
-      <c r="P10" s="39" t="e">
+      <c r="P10" s="39">
         <f>H10</f>
-        <v>#DIV/0!</v>
+        <v>60.72</v>
       </c>
       <c r="Q10" s="35" t="str">
         <f>O10</f>
         <v>mV</v>
       </c>
-      <c r="R10" s="474" t="e">
+      <c r="R10" s="474" t="str">
         <f>IF(AND(N10&lt;=H10,N10&gt;=J10),"PASSED","FAILED")</f>
-        <v>#DIV/0!</v>
+        <v>PASSED</v>
       </c>
       <c r="S10" s="474"/>
-      <c r="T10" s="39" t="e">
+      <c r="T10" s="39">
         <f>-F10+B10</f>
-        <v>#DIV/0!</v>
+        <v>59.942259838644723</v>
       </c>
       <c r="U10" s="37" t="str">
         <f>O10</f>
         <v>mV</v>
       </c>
-      <c r="V10" s="472" t="e">
+      <c r="V10" s="472" t="str">
         <f>IF(AND(T10&lt;=H10,T10&gt;=J10),"PASSED","FAILED")</f>
-        <v>#DIV/0!</v>
+        <v>PASSED</v>
       </c>
       <c r="W10" s="472"/>
-      <c r="X10" s="471" t="e">
+      <c r="X10" s="471" t="str">
         <f t="shared" ref="X10:X26" si="0">IF(AND(L10="PASSED",R10="PASSED",V10="PASSED"),"PASSED",IF(L10="FAILED","FAILED","UNDETERMINED"))</f>
-        <v>#DIV/0!</v>
+        <v>PASSED</v>
       </c>
       <c r="Y10" s="471"/>
     </row>
     <row r="11" spans="2:25">
       <c r="B11" s="43">
         <f>DataSheet!AM56</f>
-        <v>40</v>
+        <v>540</v>
       </c>
       <c r="C11" s="44" t="str">
         <f>DataSheet!P56</f>
@@ -35673,7 +35721,7 @@
       </c>
       <c r="D11" s="51">
         <f>ABS((B11*0.7%)+(3*DataSheet!CK56))</f>
-        <v>0.58000000000000007</v>
+        <v>4.08</v>
       </c>
       <c r="E11" s="35" t="str">
         <f t="shared" ref="E11:E26" si="1">C11</f>
@@ -35681,7 +35729,7 @@
       </c>
       <c r="F11" s="38">
         <f>DataSheet!DD56</f>
-        <v>80.000083443539822</v>
+        <v>5.7773206015707089E-2</v>
       </c>
       <c r="G11" s="35" t="str">
         <f t="shared" ref="G11:G26" si="2">E11</f>
@@ -35689,7 +35737,7 @@
       </c>
       <c r="H11" s="39">
         <f>DataSheet!L56+D11</f>
-        <v>540.58000000000004</v>
+        <v>544.08000000000004</v>
       </c>
       <c r="I11" s="35" t="str">
         <f t="shared" ref="I11:I26" si="3">G11</f>
@@ -35697,7 +35745,7 @@
       </c>
       <c r="J11" s="39">
         <f>DataSheet!L56-D11</f>
-        <v>539.41999999999996</v>
+        <v>535.91999999999996</v>
       </c>
       <c r="K11" s="35" t="str">
         <f t="shared" ref="K11:K26" si="4">I11</f>
@@ -35705,12 +35753,12 @@
       </c>
       <c r="L11" s="480" t="str">
         <f t="shared" ref="L11:L26" si="5">IF(AND(B11&lt;=H11,B11&gt;=J11),"PASSED","FAILED")</f>
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="M11" s="480"/>
       <c r="N11" s="39">
         <f t="shared" ref="N11:N12" si="6">F11+B11</f>
-        <v>120.00008344353982</v>
+        <v>540.05777320601567</v>
       </c>
       <c r="O11" s="40" t="str">
         <f t="shared" ref="O11:O26" si="7">G11</f>
@@ -35718,7 +35766,7 @@
       </c>
       <c r="P11" s="39">
         <f t="shared" ref="P11:P12" si="8">H11</f>
-        <v>540.58000000000004</v>
+        <v>544.08000000000004</v>
       </c>
       <c r="Q11" s="35" t="str">
         <f t="shared" ref="Q11:Q26" si="9">O11</f>
@@ -35726,12 +35774,12 @@
       </c>
       <c r="R11" s="474" t="str">
         <f t="shared" ref="R11:R26" si="10">IF(AND(N11&lt;=H11,N11&gt;=J11),"PASSED","FAILED")</f>
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="S11" s="474"/>
       <c r="T11" s="39">
         <f t="shared" ref="T11:T12" si="11">-F11+B11</f>
-        <v>-40.000083443539822</v>
+        <v>539.94222679398433</v>
       </c>
       <c r="U11" s="37" t="str">
         <f t="shared" ref="U11:U26" si="12">O11</f>
@@ -35739,12 +35787,12 @@
       </c>
       <c r="V11" s="472" t="str">
         <f t="shared" ref="V11:V26" si="13">IF(AND(T11&lt;=H11,T11&gt;=J11),"PASSED","FAILED")</f>
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="W11" s="472"/>
       <c r="X11" s="471" t="str">
         <f t="shared" si="0"/>
-        <v>FAILED</v>
+        <v>PASSED</v>
       </c>
       <c r="Y11" s="471"/>
     </row>

--- a/ASCal/template.xlsx
+++ b/ASCal/template.xlsx
@@ -497,35 +497,11 @@
     <t>6 MΩ</t>
   </si>
   <si>
-    <t>1 000 V</t>
-  </si>
-  <si>
     <t>50 MΩ</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">600 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>µ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>A</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">6 000 </t>
     </r>
     <r>
       <rPr>
@@ -600,6 +576,30 @@
   </si>
   <si>
     <t>unit</t>
+  </si>
+  <si>
+    <t>1000 V</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6000 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>µ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3352,6 +3352,25 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9"/>
         </patternFill>
       </fill>
@@ -3812,13 +3831,6 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i/>
@@ -4160,18 +4172,6 @@
         <i/>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -7630,7 +7630,7 @@
     <row r="35" spans="1:27" s="54" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="53"/>
       <c r="C35" s="281" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D35" s="281"/>
       <c r="E35" s="281"/>
@@ -7891,19 +7891,19 @@
     <row r="49" spans="1:23" s="58" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="57"/>
       <c r="C49" s="58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="56"/>
       <c r="C50" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="51" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="56"/>
       <c r="C51" s="26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O51" s="251">
         <f>EDATE(DataSheet!AL11,12)</f>
@@ -7953,7 +7953,7 @@
       <c r="J55" s="228"/>
       <c r="K55" s="228"/>
       <c r="S55" s="228" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T55" s="228"/>
       <c r="U55" s="228"/>
@@ -8553,7 +8553,7 @@
       <c r="C84" s="19"/>
       <c r="E84" s="238" t="str">
         <f>DataSheet!F69</f>
-        <v>1 000 V</v>
+        <v>1000 V</v>
       </c>
       <c r="F84" s="238"/>
       <c r="G84" s="238"/>
@@ -9945,7 +9945,7 @@
       <c r="D140" s="29"/>
       <c r="E140" s="238" t="str">
         <f>DataSheet!F94</f>
-        <v>1 000 V</v>
+        <v>1000 V</v>
       </c>
       <c r="F140" s="238"/>
       <c r="G140" s="238"/>
@@ -10212,7 +10212,7 @@
       <c r="A149" s="60"/>
       <c r="E149" s="288" t="str">
         <f>DataSheet!F114</f>
-        <v>6 000 µA</v>
+        <v>6000 µA</v>
       </c>
       <c r="F149" s="289"/>
       <c r="G149" s="289"/>
@@ -10757,7 +10757,7 @@
     <row r="177" spans="5:24" ht="15" customHeight="1">
       <c r="E177" s="232" t="str">
         <f>DataSheet!F128</f>
-        <v>6 000 µA</v>
+        <v>6000 µA</v>
       </c>
       <c r="F177" s="233"/>
       <c r="G177" s="233"/>
@@ -15933,16 +15933,16 @@
       <c r="Z55" s="291"/>
       <c r="AA55" s="291"/>
       <c r="AB55" s="291"/>
-      <c r="AC55" s="291"/>
-      <c r="AD55" s="291"/>
-      <c r="AE55" s="291"/>
-      <c r="AF55" s="291"/>
-      <c r="AG55" s="291"/>
-      <c r="AH55" s="291"/>
-      <c r="AI55" s="291"/>
-      <c r="AJ55" s="291"/>
-      <c r="AK55" s="291"/>
-      <c r="AL55" s="291"/>
+      <c r="AC55" s="325"/>
+      <c r="AD55" s="326"/>
+      <c r="AE55" s="326"/>
+      <c r="AF55" s="326"/>
+      <c r="AG55" s="327"/>
+      <c r="AH55" s="325"/>
+      <c r="AI55" s="326"/>
+      <c r="AJ55" s="326"/>
+      <c r="AK55" s="326"/>
+      <c r="AL55" s="327"/>
       <c r="AM55" s="291" t="e">
         <f t="shared" ref="AM55:AM68" si="0">AVERAGE(X55:AL55)</f>
         <v>#DIV/0!</v>
@@ -16106,7 +16106,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="DE55" s="178" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:109" s="174" customFormat="1" ht="18" customHeight="1">
@@ -19005,7 +19005,7 @@
       <c r="D69" s="139"/>
       <c r="E69" s="139"/>
       <c r="F69" s="310" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G69" s="311"/>
       <c r="H69" s="311"/>
@@ -24207,7 +24207,7 @@
       <c r="D94" s="139"/>
       <c r="E94" s="139"/>
       <c r="F94" s="310" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="G94" s="311"/>
       <c r="H94" s="311"/>
@@ -26972,7 +26972,7 @@
       <c r="D108" s="139"/>
       <c r="E108" s="139"/>
       <c r="F108" s="296" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G108" s="294"/>
       <c r="H108" s="294"/>
@@ -27700,7 +27700,7 @@
       <c r="D113" s="139"/>
       <c r="E113" s="139"/>
       <c r="F113" s="293" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G113" s="294"/>
       <c r="H113" s="294"/>
@@ -27715,7 +27715,7 @@
       <c r="N113" s="298"/>
       <c r="O113" s="298"/>
       <c r="P113" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q113" s="299"/>
       <c r="R113" s="300"/>
@@ -27924,7 +27924,7 @@
       <c r="D114" s="139"/>
       <c r="E114" s="139"/>
       <c r="F114" s="293" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="G114" s="294"/>
       <c r="H114" s="294"/>
@@ -27939,7 +27939,7 @@
       <c r="N114" s="298"/>
       <c r="O114" s="298"/>
       <c r="P114" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q114" s="299"/>
       <c r="R114" s="300"/>
@@ -28148,7 +28148,7 @@
       <c r="D115" s="139"/>
       <c r="E115" s="139"/>
       <c r="F115" s="293" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G115" s="294"/>
       <c r="H115" s="294"/>
@@ -28594,7 +28594,7 @@
       <c r="D117" s="139"/>
       <c r="E117" s="139"/>
       <c r="F117" s="304" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G117" s="305"/>
       <c r="H117" s="305"/>
@@ -28833,7 +28833,7 @@
       <c r="N118" s="298"/>
       <c r="O118" s="298"/>
       <c r="P118" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q118" s="299"/>
       <c r="R118" s="300"/>
@@ -29055,7 +29055,7 @@
       <c r="N119" s="298"/>
       <c r="O119" s="298"/>
       <c r="P119" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q119" s="299"/>
       <c r="R119" s="300"/>
@@ -29279,7 +29279,7 @@
       <c r="N120" s="298"/>
       <c r="O120" s="298"/>
       <c r="P120" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q120" s="299"/>
       <c r="R120" s="300"/>
@@ -29501,7 +29501,7 @@
       <c r="N121" s="298"/>
       <c r="O121" s="298"/>
       <c r="P121" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q121" s="299"/>
       <c r="R121" s="300"/>
@@ -30215,7 +30215,7 @@
       <c r="D126" s="139"/>
       <c r="E126" s="139"/>
       <c r="F126" s="293" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G126" s="294"/>
       <c r="H126" s="294"/>
@@ -30230,7 +30230,7 @@
       <c r="N126" s="298"/>
       <c r="O126" s="298"/>
       <c r="P126" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q126" s="299"/>
       <c r="R126" s="300"/>
@@ -30452,7 +30452,7 @@
       <c r="N127" s="298"/>
       <c r="O127" s="298"/>
       <c r="P127" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q127" s="299"/>
       <c r="R127" s="300"/>
@@ -30661,7 +30661,7 @@
       <c r="D128" s="139"/>
       <c r="E128" s="139"/>
       <c r="F128" s="293" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="G128" s="294"/>
       <c r="H128" s="294"/>
@@ -30676,7 +30676,7 @@
       <c r="N128" s="298"/>
       <c r="O128" s="298"/>
       <c r="P128" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q128" s="299"/>
       <c r="R128" s="300"/>
@@ -30898,7 +30898,7 @@
       <c r="N129" s="298"/>
       <c r="O129" s="298"/>
       <c r="P129" s="299" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="Q129" s="299"/>
       <c r="R129" s="300"/>
@@ -31107,7 +31107,7 @@
       <c r="D130" s="139"/>
       <c r="E130" s="139"/>
       <c r="F130" s="293" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G130" s="294"/>
       <c r="H130" s="294"/>
@@ -31553,7 +31553,7 @@
       <c r="D132" s="139"/>
       <c r="E132" s="139"/>
       <c r="F132" s="304" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G132" s="305"/>
       <c r="H132" s="305"/>
@@ -32014,7 +32014,7 @@
       <c r="N134" s="298"/>
       <c r="O134" s="298"/>
       <c r="P134" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q134" s="299"/>
       <c r="R134" s="300"/>
@@ -32236,7 +32236,7 @@
       <c r="N135" s="298"/>
       <c r="O135" s="298"/>
       <c r="P135" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q135" s="299"/>
       <c r="R135" s="300"/>
@@ -32460,7 +32460,7 @@
       <c r="N136" s="298"/>
       <c r="O136" s="298"/>
       <c r="P136" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q136" s="299"/>
       <c r="R136" s="300"/>
@@ -32682,7 +32682,7 @@
       <c r="N137" s="298"/>
       <c r="O137" s="298"/>
       <c r="P137" s="299" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q137" s="299"/>
       <c r="R137" s="300"/>
@@ -33042,7 +33042,7 @@
     <row r="140" spans="1:109" s="143" customFormat="1" ht="13.5">
       <c r="A140" s="136"/>
       <c r="B140" s="429" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C140" s="430"/>
       <c r="D140" s="430"/>
@@ -33361,7 +33361,7 @@
     <row r="144" spans="1:109" s="143" customFormat="1" ht="13.5">
       <c r="A144" s="136"/>
       <c r="B144" s="423" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C144" s="424"/>
       <c r="D144" s="424"/>
@@ -35160,466 +35160,466 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P55 X55:AV55 X56:AL71">
-    <cfRule type="expression" dxfId="108" priority="457">
+    <cfRule type="expression" dxfId="1" priority="457">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P56:R56 X56:AV56">
-    <cfRule type="expression" dxfId="107" priority="456">
+    <cfRule type="expression" dxfId="108" priority="456">
       <formula>$BQ$56="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P57:R57 X57:AV57">
-    <cfRule type="expression" dxfId="106" priority="455">
+    <cfRule type="expression" dxfId="107" priority="455">
       <formula>$BQ$57="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P58:R58 X58:AV58">
-    <cfRule type="expression" dxfId="105" priority="454">
+    <cfRule type="expression" dxfId="106" priority="454">
       <formula>$BQ$58="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P59:R59 X59:AV59">
-    <cfRule type="expression" dxfId="104" priority="453">
+    <cfRule type="expression" dxfId="105" priority="453">
       <formula>$BQ$59="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P60:R60 X60:AV60">
-    <cfRule type="expression" dxfId="103" priority="452">
+    <cfRule type="expression" dxfId="104" priority="452">
       <formula>$BQ$60="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P62:R62 X62:AV62">
-    <cfRule type="expression" dxfId="102" priority="450">
+    <cfRule type="expression" dxfId="103" priority="450">
       <formula>$BQ$62="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P63:R63 X63:AV63">
-    <cfRule type="expression" dxfId="101" priority="449">
+    <cfRule type="expression" dxfId="102" priority="449">
       <formula>$BQ$63="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P64:R64 X64:AV64">
-    <cfRule type="expression" dxfId="100" priority="448">
+    <cfRule type="expression" dxfId="101" priority="448">
       <formula>$BQ$64="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P65:R65 X65:AV65">
-    <cfRule type="expression" dxfId="99" priority="447">
+    <cfRule type="expression" dxfId="100" priority="447">
       <formula>$BQ$65="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P70:R70">
-    <cfRule type="expression" dxfId="98" priority="163">
+    <cfRule type="expression" dxfId="99" priority="163">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P71:R71">
-    <cfRule type="expression" dxfId="97" priority="162">
+    <cfRule type="expression" dxfId="98" priority="162">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P85:R85 AM85:AV85">
-    <cfRule type="expression" dxfId="96" priority="435">
+    <cfRule type="expression" dxfId="97" priority="435">
       <formula>$BQ$85="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P87:R87 AM87:AV87">
-    <cfRule type="expression" dxfId="95" priority="433">
+    <cfRule type="expression" dxfId="96" priority="433">
       <formula>$BQ$87="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P89:R89 AM89:AV89">
-    <cfRule type="expression" dxfId="94" priority="431">
+    <cfRule type="expression" dxfId="95" priority="431">
       <formula>$BQ$89="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P95:R95 AM95:AV95">
-    <cfRule type="expression" dxfId="93" priority="155">
+    <cfRule type="expression" dxfId="94" priority="155">
       <formula>$BQ$91="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P97:R97 AM97:AV97">
-    <cfRule type="expression" dxfId="92" priority="153">
+    <cfRule type="expression" dxfId="93" priority="153">
       <formula>$BQ$93="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P113:R114">
-    <cfRule type="expression" dxfId="91" priority="123">
+    <cfRule type="expression" dxfId="92" priority="123">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P115:R115">
-    <cfRule type="expression" dxfId="90" priority="146">
+    <cfRule type="expression" dxfId="91" priority="146">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P116:R116">
-    <cfRule type="expression" dxfId="89" priority="145">
+    <cfRule type="expression" dxfId="90" priority="145">
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P117:R117">
-    <cfRule type="expression" dxfId="88" priority="139">
+    <cfRule type="expression" dxfId="89" priority="139">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P132:R132">
-    <cfRule type="expression" dxfId="87" priority="115">
+    <cfRule type="expression" dxfId="88" priority="115">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P133:R133">
-    <cfRule type="expression" dxfId="86" priority="114">
+    <cfRule type="expression" dxfId="87" priority="114">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P80:W80 AM80:AV80">
-    <cfRule type="expression" dxfId="85" priority="440">
+    <cfRule type="expression" dxfId="86" priority="440">
       <formula>$BQ$80="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P81:W81 AM81:AV81">
-    <cfRule type="expression" dxfId="84" priority="181">
+    <cfRule type="expression" dxfId="85" priority="181">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P82:W82 AM82:AV82">
-    <cfRule type="expression" dxfId="83" priority="438">
+    <cfRule type="expression" dxfId="84" priority="438">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P86:W86 AM86:AV86">
-    <cfRule type="expression" dxfId="82" priority="434">
+    <cfRule type="expression" dxfId="83" priority="434">
       <formula>$BQ$86="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P88:W88 AM88:AV88">
-    <cfRule type="expression" dxfId="81" priority="432">
+    <cfRule type="expression" dxfId="82" priority="432">
       <formula>$BQ$88="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P96:W96 AM96:AV96">
-    <cfRule type="expression" dxfId="80" priority="154">
+    <cfRule type="expression" dxfId="81" priority="154">
       <formula>$BQ$92="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P130:W130 AM130:AV130">
-    <cfRule type="expression" dxfId="79" priority="117">
+    <cfRule type="expression" dxfId="80" priority="117">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P131:W131 AM131:AV131">
-    <cfRule type="expression" dxfId="78" priority="43">
+    <cfRule type="expression" dxfId="79" priority="43">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S79:W79">
-    <cfRule type="expression" dxfId="77" priority="182">
+    <cfRule type="expression" dxfId="78" priority="182">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S83:W83">
-    <cfRule type="expression" dxfId="76" priority="180">
+    <cfRule type="expression" dxfId="77" priority="180">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S85:W85">
-    <cfRule type="expression" dxfId="75" priority="179">
+    <cfRule type="expression" dxfId="76" priority="179">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S87:W87">
-    <cfRule type="expression" dxfId="74" priority="178">
+    <cfRule type="expression" dxfId="75" priority="178">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S89:W89">
-    <cfRule type="expression" dxfId="73" priority="177">
+    <cfRule type="expression" dxfId="74" priority="177">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S91:W91">
-    <cfRule type="expression" dxfId="72" priority="176">
+    <cfRule type="expression" dxfId="73" priority="176">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S93:W93">
-    <cfRule type="expression" dxfId="71" priority="175">
+    <cfRule type="expression" dxfId="72" priority="175">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S95:W95">
-    <cfRule type="expression" dxfId="70" priority="152">
+    <cfRule type="expression" dxfId="71" priority="152">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S97:W97">
-    <cfRule type="expression" dxfId="69" priority="151">
+    <cfRule type="expression" dxfId="70" priority="151">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S128:W128">
-    <cfRule type="expression" dxfId="68" priority="56">
+    <cfRule type="expression" dxfId="69" priority="56">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S129:W129">
-    <cfRule type="expression" dxfId="67" priority="46">
+    <cfRule type="expression" dxfId="68" priority="46">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S132:W132">
-    <cfRule type="expression" dxfId="66" priority="89">
+    <cfRule type="expression" dxfId="67" priority="89">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S133:W133">
-    <cfRule type="expression" dxfId="65" priority="42">
+    <cfRule type="expression" dxfId="66" priority="42">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S136:W136">
-    <cfRule type="expression" dxfId="64" priority="184">
+    <cfRule type="expression" dxfId="65" priority="184">
       <formula>$BQ$134="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S137:W137">
-    <cfRule type="expression" dxfId="63" priority="40">
+    <cfRule type="expression" dxfId="64" priority="40">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S77:W77 AM77:AV77">
-    <cfRule type="expression" dxfId="62" priority="239">
+    <cfRule type="expression" dxfId="63" priority="239">
       <formula>$BQ$81="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S78:W78 AM78:AV78">
-    <cfRule type="expression" dxfId="61" priority="238">
+    <cfRule type="expression" dxfId="62" priority="238">
       <formula>$BQ$82="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S127:W127 AM127:AV127">
-    <cfRule type="expression" dxfId="60" priority="83">
+    <cfRule type="expression" dxfId="61" priority="83">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S135:W135 AM135:AV135">
-    <cfRule type="expression" dxfId="59" priority="41">
+    <cfRule type="expression" dxfId="60" priority="41">
       <formula>$BQ$135="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X55:AL71">
-    <cfRule type="notContainsBlanks" dxfId="58" priority="170">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="170">
       <formula>LEN(TRIM(X55))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X66:AV66">
-    <cfRule type="expression" dxfId="57" priority="446">
+    <cfRule type="expression" dxfId="59" priority="446">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X67:AV67">
-    <cfRule type="expression" dxfId="56" priority="445">
+    <cfRule type="expression" dxfId="58" priority="445">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X68:AV68">
-    <cfRule type="expression" dxfId="55" priority="444">
+    <cfRule type="expression" dxfId="57" priority="444">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X69:AV69">
-    <cfRule type="expression" dxfId="54" priority="167">
+    <cfRule type="expression" dxfId="56" priority="167">
       <formula>$BQ$66="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X70:AV70">
-    <cfRule type="expression" dxfId="53" priority="166">
+    <cfRule type="expression" dxfId="55" priority="166">
       <formula>$BQ$67="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X71:AV71">
-    <cfRule type="expression" dxfId="52" priority="165">
+    <cfRule type="expression" dxfId="54" priority="165">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P83:R83 AM79:AV79 AM83:AV83">
-    <cfRule type="expression" dxfId="51" priority="437">
+    <cfRule type="expression" dxfId="53" priority="437">
       <formula>$BQ$83="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM106:AV107">
-    <cfRule type="expression" dxfId="50" priority="418">
+    <cfRule type="expression" dxfId="52" priority="418">
       <formula>$BQ$106="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM108:AV108">
-    <cfRule type="expression" dxfId="49" priority="417">
+    <cfRule type="expression" dxfId="51" priority="417">
       <formula>$BQ$108="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM113:AV113">
-    <cfRule type="expression" dxfId="48" priority="134">
+    <cfRule type="expression" dxfId="50" priority="134">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM114:AV114">
-    <cfRule type="expression" dxfId="47" priority="132">
+    <cfRule type="expression" dxfId="49" priority="132">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM115:AV115 AM118:AV118">
-    <cfRule type="expression" dxfId="46" priority="415">
+    <cfRule type="expression" dxfId="48" priority="415">
       <formula>$BQ$118="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM116:AV116 AM119:AV119">
-    <cfRule type="expression" dxfId="45" priority="414">
+    <cfRule type="expression" dxfId="47" priority="414">
       <formula>$BQ$119="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM120:AV121 AM117:AV117">
-    <cfRule type="expression" dxfId="44" priority="413">
+    <cfRule type="expression" dxfId="46" priority="413">
       <formula>$BQ$121="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM128:AV128">
-    <cfRule type="expression" dxfId="43" priority="87">
+    <cfRule type="expression" dxfId="45" priority="87">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM129:AV129">
-    <cfRule type="expression" dxfId="42" priority="86">
+    <cfRule type="expression" dxfId="44" priority="86">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM132:AV132 AM136:AV136">
-    <cfRule type="expression" dxfId="41" priority="410">
+    <cfRule type="expression" dxfId="43" priority="410">
       <formula>$BQ$136="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM133:AV133 AM137:AV137">
-    <cfRule type="expression" dxfId="40" priority="409">
+    <cfRule type="expression" dxfId="42" priority="409">
       <formula>$BQ$137="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ56:BU71">
-    <cfRule type="containsText" dxfId="39" priority="168" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="41" priority="168" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ56)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="169" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="40" priority="169" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ56)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ76:BU97">
-    <cfRule type="containsText" dxfId="37" priority="158" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="39" priority="158" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ76)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="157" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="38" priority="157" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ76)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ102:BU108">
-    <cfRule type="containsText" dxfId="35" priority="172" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="37" priority="172" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ102)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="173" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="36" priority="173" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ102)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ113:BU121">
-    <cfRule type="containsText" dxfId="33" priority="122" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="35" priority="122" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ113)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="121" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="34" priority="121" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ126:BU137">
-    <cfRule type="containsText" dxfId="31" priority="80" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="33" priority="80" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ126)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="79" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="32" priority="79" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ126)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X57:AL57">
-    <cfRule type="expression" dxfId="29" priority="17">
+    <cfRule type="expression" dxfId="31" priority="17">
       <formula>$BQ$56="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ55:BU55">
-    <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="PASS">
+    <cfRule type="containsText" dxfId="30" priority="13" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",BQ55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="27" priority="14" operator="containsText" text="FAIL">
+    <cfRule type="containsText" dxfId="29" priority="14" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",BQ55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X76:AL97">
-    <cfRule type="expression" dxfId="26" priority="12">
+    <cfRule type="expression" dxfId="28" priority="12">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X76:AL97">
-    <cfRule type="notContainsBlanks" dxfId="25" priority="11">
+    <cfRule type="notContainsBlanks" dxfId="27" priority="11">
       <formula>LEN(TRIM(X76))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X76:AL97">
-    <cfRule type="expression" dxfId="24" priority="10">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X102:AL108">
-    <cfRule type="expression" dxfId="23" priority="9">
+    <cfRule type="expression" dxfId="25" priority="9">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X102:AL108">
-    <cfRule type="notContainsBlanks" dxfId="22" priority="8">
+    <cfRule type="notContainsBlanks" dxfId="24" priority="8">
       <formula>LEN(TRIM(X102))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X102:AL108">
-    <cfRule type="expression" dxfId="21" priority="7">
+    <cfRule type="expression" dxfId="23" priority="7">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X113:AL121">
-    <cfRule type="expression" dxfId="20" priority="6">
+    <cfRule type="expression" dxfId="22" priority="6">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X113:AL121">
-    <cfRule type="notContainsBlanks" dxfId="19" priority="5">
+    <cfRule type="notContainsBlanks" dxfId="21" priority="5">
       <formula>LEN(TRIM(X113))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X113:AL121">
-    <cfRule type="expression" dxfId="18" priority="4">
+    <cfRule type="expression" dxfId="20" priority="4">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X126:AL137">
-    <cfRule type="expression" dxfId="17" priority="3">
+    <cfRule type="expression" dxfId="19" priority="3">
       <formula>$BQ$55="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X126:AL137">
-    <cfRule type="notContainsBlanks" dxfId="16" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="18" priority="2">
       <formula>LEN(TRIM(X126))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X126:AL137">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$BQ$68="FAIL"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0.51181102362204722" header="0" footer="0"/>
-  <pageSetup paperSize="10000" scale="85" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;L&amp;"Arial Narrow,Regular"&amp;9Page &amp;P of &amp;N&amp;R&amp;"Arial Narrow,Regular"&amp;9 7F-04-02 Rev. 02
 Effectivity Date: August 01, 2019</oddFooter>
@@ -40791,10 +40791,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L10:L26">
-    <cfRule type="containsText" dxfId="14" priority="104" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="16" priority="104" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",L10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="105" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="15" priority="105" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",L10)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -40811,10 +40811,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L31:L48">
-    <cfRule type="containsText" dxfId="12" priority="101" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="14" priority="101" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",L31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="102" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="13" priority="102" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",L31)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="103">
@@ -40829,10 +40829,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L53:L59">
-    <cfRule type="containsText" dxfId="10" priority="98" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="12" priority="98" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",L53)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="99" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="11" priority="99" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",L53)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="100">
@@ -40847,10 +40847,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L64:L66">
-    <cfRule type="containsText" dxfId="8" priority="95" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="10" priority="95" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",L64)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="96" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="9" priority="96" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",L64)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="97">
@@ -40865,10 +40865,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L71:L74">
-    <cfRule type="containsText" dxfId="6" priority="92" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="8" priority="92" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",L71)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="93" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="7" priority="93" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",L71)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="94">
@@ -40883,23 +40883,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R10:S26 R31:S48 R53:S59 R64:S66 R71:S74">
-    <cfRule type="containsText" dxfId="4" priority="90" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="6" priority="90" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",R10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="91" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="5" priority="91" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",R10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V10:Y26 V31:Y48 V53:Y59 V64:Y66 V71:Y74">
-    <cfRule type="containsText" dxfId="2" priority="32" operator="containsText" text="FAILED">
+    <cfRule type="containsText" dxfId="4" priority="32" operator="containsText" text="FAILED">
       <formula>NOT(ISERROR(SEARCH("FAILED",V10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="33" operator="containsText" text="PASSED">
+    <cfRule type="containsText" dxfId="3" priority="33" operator="containsText" text="PASSED">
       <formula>NOT(ISERROR(SEARCH("PASSED",V10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X10:Y26 X31:Y48 X53:Y59 X64:Y66 X71:Y74">
-    <cfRule type="containsText" dxfId="0" priority="31" operator="containsText" text="UNDETERMINED">
+    <cfRule type="containsText" dxfId="2" priority="31" operator="containsText" text="UNDETERMINED">
       <formula>NOT(ISERROR(SEARCH("UNDETERMINED",X10)))</formula>
     </cfRule>
   </conditionalFormatting>
